--- a/label.xlsx
+++ b/label.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D66EF65-C59E-4ACD-A3B0-A4F603823BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="1380" windowWidth="14400" windowHeight="15750" xr2:uid="{39AF3F03-114A-47C0-9B27-B86DFB102F01}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15750" xr2:uid="{39AF3F03-114A-47C0-9B27-B86DFB102F01}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
